--- a/docs/downloads/13/tbl_synthese_qualite_marovoay_maroala.xlsx
+++ b/docs/downloads/13/tbl_synthese_qualite_marovoay_maroala.xlsx
@@ -392,9 +392,6 @@
           <t>Neutre</t>
         </is>
       </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
